--- a/forms/trg/Formulir_TRG_biodental-engineering.xlsx
+++ b/forms/trg/Formulir_TRG_biodental-engineering.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Kedokteran gigi &amp; kesehatan mulut</t>
+          <t>Biomedis &amp; kedokteran regeneratif</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1650,7 +1650,7 @@
     <row r="6">
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Biomedis &amp; kedokteran regeneratif</t>
+          <t>Kedokteran gigi &amp; kesehatan mulut</t>
         </is>
       </c>
     </row>

--- a/forms/trg/Formulir_TRG_biodental-engineering.xlsx
+++ b/forms/trg/Formulir_TRG_biodental-engineering.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,29 +925,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Taufiqqurrahman,S.T.,M.T</t>
+          <t>Nurlindah Hamrun</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Machine Engineering</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Material composit strengthness</t>
+          <t>Biomarine in dentistry</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6000-7480%20View%20this%20author’s%20ORCID%20profile</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
@@ -962,16 +962,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Herlina Rante</t>
+          <t>Taufiqqurrahman,S.T.,M.T</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Machine Engineering</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Material composit strengthness</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
@@ -991,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Erni Marlina</t>
+          <t>Herlina Rante</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1020,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Arifin</t>
+          <t>Erni Marlina</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1049,12 +1057,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Irfan Sugianto</t>
+          <t>Arifin</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1078,12 +1086,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rusdina Bte Ladju</t>
+          <t>Irfan Sugianto</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1107,33 +1115,21 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ruslin</t>
+          <t>Rusdina Bte Ladju</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>HASANUDDIN UNIVERSITY</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Oral Maxillofacial Surgeon</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0943-4000%20View%20this%20author’s%20ORCID%20profile</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
@@ -1148,12 +1144,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sri Oktawati</t>
+          <t>Muhammad Ruslin</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1163,14 +1159,18 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Periodontist</t>
+          <t>Oral Maxillofacial Surgeon</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0943-4000%20View%20this%20author’s%20ORCID%20profile</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1185,16 +1185,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Emilio Satoshi Hara</t>
+          <t>Sri Oktawati</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>HASANUDDIN UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Periodontist</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1214,29 +1222,21 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>A.St. Hajrah Yusuf</t>
+          <t>Emilio Satoshi Hara</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>HASANUDDIN UNIVERSITY_NIIGATA UNIVERSITY</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3010-4524%20View%20this%20author’s%20ORCID%20profile</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fadil Hidayat</t>
+          <t>A.St. Hajrah Yusuf</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1261,19 +1261,19 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Oral and Maxillofacial Radiology</t>
-        </is>
-      </c>
+          <t>HASANUDDIN UNIVERSITY_NIIGATA UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3010-4524%20View%20this%20author’s%20ORCID%20profile</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Filzah Azalia</t>
+          <t>Muhammad Fadil Hidayat</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1296,10 +1296,14 @@
           <t>Researcher</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>King\'s College London</t>
+          <t>Oral and Maxillofacial Radiology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1321,16 +1325,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Ainiyyah Fildza Zaizafun</t>
+          <t>Filzah Azalia</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>King\'s College London</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1350,12 +1358,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Ardian Jayakusuma</t>
+          <t>Ainiyyah Fildza Zaizafun</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1377,10 +1385,22 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Ardian Jayakusuma</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>To revolutionize dental tissue engineering by harnessing the potential of natural materials, particularly marine biota, to develop innovative and sustainable solutions for addressing alveolar bone loss. We aim to advance scientific knowledge, foster interdisciplinary collaboration, and translate research into practical, eco-conscious applications that improve patient outcomes and contribute to the responsible utilization of marine biodiversity</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1388,7 +1408,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1577,15 +1601,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
